--- a/판매량(계획_실적).xlsx
+++ b/판매량(계획_실적).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_최종\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9DDFD4-0865-4151-9D8C-DBB243CB62E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3775180-0AD1-49B0-BF8A-0558BA371C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
   </bookViews>
@@ -284,14 +284,7 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -24009,6 +24002,51 @@
       <c r="C136" s="11">
         <v>3</v>
       </c>
+      <c r="D136" s="15">
+        <v>482.46820629999996</v>
+      </c>
+      <c r="E136" s="15">
+        <v>93521.836925299998</v>
+      </c>
+      <c r="F136" s="15">
+        <v>1632.0379452</v>
+      </c>
+      <c r="G136" s="15">
+        <v>961.56100000000004</v>
+      </c>
+      <c r="H136" s="15">
+        <v>96597.904076799998</v>
+      </c>
+      <c r="I136" s="15">
+        <v>7419.2333662000001</v>
+      </c>
+      <c r="J136" s="15">
+        <v>2364.7733560000001</v>
+      </c>
+      <c r="K136" s="15">
+        <v>2216.6000800000002</v>
+      </c>
+      <c r="L136" s="15">
+        <v>17201.319387800002</v>
+      </c>
+      <c r="M136" s="15">
+        <v>5765</v>
+      </c>
+      <c r="N136" s="15">
+        <v>303</v>
+      </c>
+      <c r="O136" s="15">
+        <v>530.86699999999996</v>
+      </c>
+      <c r="P136" s="15">
+        <v>428.04140699999999</v>
+      </c>
+      <c r="Q136" s="15">
+        <v>18.167999999999999</v>
+      </c>
+      <c r="R136" s="15">
+        <v>177.08759380000001</v>
+      </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" s="13">
@@ -32070,6 +32108,51 @@
       <c r="C136" s="11">
         <v>3</v>
       </c>
+      <c r="D136" s="15">
+        <v>20553</v>
+      </c>
+      <c r="E136" s="15">
+        <v>3994456</v>
+      </c>
+      <c r="F136" s="15">
+        <v>69757</v>
+      </c>
+      <c r="G136" s="15">
+        <v>41082</v>
+      </c>
+      <c r="H136" s="15">
+        <v>4125848</v>
+      </c>
+      <c r="I136" s="15">
+        <v>317079</v>
+      </c>
+      <c r="J136" s="15">
+        <v>101065</v>
+      </c>
+      <c r="K136" s="15">
+        <v>94770</v>
+      </c>
+      <c r="L136" s="15">
+        <v>735283</v>
+      </c>
+      <c r="M136" s="15">
+        <v>248779</v>
+      </c>
+      <c r="N136" s="15">
+        <v>12806</v>
+      </c>
+      <c r="O136" s="15">
+        <v>22681</v>
+      </c>
+      <c r="P136" s="15">
+        <v>18292</v>
+      </c>
+      <c r="Q136" s="15">
+        <v>776</v>
+      </c>
+      <c r="R136" s="15">
+        <v>7566</v>
+      </c>
     </row>
     <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137" s="13">

--- a/판매량(계획_실적).xlsx
+++ b/판매량(계획_실적).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_최종\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3775180-0AD1-49B0-BF8A-0558BA371C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA531451-3813-4D2A-8507-9C84B227A95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
   </bookViews>
   <sheets>
     <sheet name="계획_부피" sheetId="1" r:id="rId1"/>
@@ -24058,6 +24058,51 @@
       <c r="C137" s="12">
         <v>4</v>
       </c>
+      <c r="D137" s="15">
+        <v>448.3878378</v>
+      </c>
+      <c r="E137" s="15">
+        <v>67397.668002699997</v>
+      </c>
+      <c r="F137" s="15">
+        <v>1025.4338680000001</v>
+      </c>
+      <c r="G137" s="15">
+        <v>426.05200000000002</v>
+      </c>
+      <c r="H137" s="15">
+        <v>69297.541708499979</v>
+      </c>
+      <c r="I137" s="15">
+        <v>7666.9325200999992</v>
+      </c>
+      <c r="J137" s="15">
+        <v>1643.8408836999999</v>
+      </c>
+      <c r="K137" s="15">
+        <v>1081.9660890000002</v>
+      </c>
+      <c r="L137" s="15">
+        <v>18609.036172799995</v>
+      </c>
+      <c r="M137" s="15">
+        <v>5747</v>
+      </c>
+      <c r="N137" s="15">
+        <v>297</v>
+      </c>
+      <c r="O137" s="15">
+        <v>436.22300000000001</v>
+      </c>
+      <c r="P137" s="15">
+        <v>419.11853079999997</v>
+      </c>
+      <c r="Q137" s="15">
+        <v>15.920999999999999</v>
+      </c>
+      <c r="R137" s="15">
+        <v>73.101049199999991</v>
+      </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" s="10">
@@ -32164,6 +32209,51 @@
       <c r="C137" s="12">
         <v>4</v>
       </c>
+      <c r="D137" s="15">
+        <v>19147</v>
+      </c>
+      <c r="E137" s="15">
+        <v>2877534</v>
+      </c>
+      <c r="F137" s="15">
+        <v>43732</v>
+      </c>
+      <c r="G137" s="15">
+        <v>18180</v>
+      </c>
+      <c r="H137" s="15">
+        <v>2958593</v>
+      </c>
+      <c r="I137" s="15">
+        <v>327092</v>
+      </c>
+      <c r="J137" s="15">
+        <v>70133</v>
+      </c>
+      <c r="K137" s="15">
+        <v>46145</v>
+      </c>
+      <c r="L137" s="15">
+        <v>793601</v>
+      </c>
+      <c r="M137" s="15">
+        <v>247986</v>
+      </c>
+      <c r="N137" s="15">
+        <v>12554</v>
+      </c>
+      <c r="O137" s="15">
+        <v>18612</v>
+      </c>
+      <c r="P137" s="15">
+        <v>17879</v>
+      </c>
+      <c r="Q137" s="15">
+        <v>679</v>
+      </c>
+      <c r="R137" s="15">
+        <v>3119</v>
+      </c>
     </row>
     <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138" s="10">

--- a/판매량(계획_실적).xlsx
+++ b/판매량(계획_실적).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_최종\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA531451-3813-4D2A-8507-9C84B227A95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5966A0BF-2C69-422E-94E2-A5F14C064F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
   </bookViews>
   <sheets>
     <sheet name="계획_부피" sheetId="1" r:id="rId1"/>
@@ -24114,6 +24114,51 @@
       <c r="C138" s="11">
         <v>5</v>
       </c>
+      <c r="D138" s="15">
+        <v>440.89627669999999</v>
+      </c>
+      <c r="E138" s="15">
+        <v>33309.412546599997</v>
+      </c>
+      <c r="F138" s="15">
+        <v>536.73900380000009</v>
+      </c>
+      <c r="G138" s="15">
+        <v>207.202</v>
+      </c>
+      <c r="H138" s="15">
+        <v>34494.249827099993</v>
+      </c>
+      <c r="I138" s="15">
+        <v>6815.1585821999997</v>
+      </c>
+      <c r="J138" s="15">
+        <v>847.32848559999991</v>
+      </c>
+      <c r="K138" s="15">
+        <v>727.10402040000008</v>
+      </c>
+      <c r="L138" s="15">
+        <v>17076.293895399998</v>
+      </c>
+      <c r="M138" s="15">
+        <v>5934</v>
+      </c>
+      <c r="N138" s="15">
+        <v>307</v>
+      </c>
+      <c r="O138" s="15">
+        <v>410.10199999999998</v>
+      </c>
+      <c r="P138" s="15">
+        <v>407.04349540000004</v>
+      </c>
+      <c r="Q138" s="15">
+        <v>13.486000000000001</v>
+      </c>
+      <c r="R138" s="15">
+        <v>53.322677400000003</v>
+      </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" s="13">
@@ -32265,6 +32310,51 @@
       <c r="C138" s="11">
         <v>5</v>
       </c>
+      <c r="D138" s="15">
+        <v>18820</v>
+      </c>
+      <c r="E138" s="15">
+        <v>1421534</v>
+      </c>
+      <c r="F138" s="15">
+        <v>22906</v>
+      </c>
+      <c r="G138" s="15">
+        <v>8835</v>
+      </c>
+      <c r="H138" s="15">
+        <v>1472095</v>
+      </c>
+      <c r="I138" s="15">
+        <v>290934</v>
+      </c>
+      <c r="J138" s="15">
+        <v>36176</v>
+      </c>
+      <c r="K138" s="15">
+        <v>31043</v>
+      </c>
+      <c r="L138" s="15">
+        <v>728853</v>
+      </c>
+      <c r="M138" s="15">
+        <v>256073</v>
+      </c>
+      <c r="N138" s="15">
+        <v>12975</v>
+      </c>
+      <c r="O138" s="15">
+        <v>17486</v>
+      </c>
+      <c r="P138" s="15">
+        <v>17361</v>
+      </c>
+      <c r="Q138" s="15">
+        <v>575</v>
+      </c>
+      <c r="R138" s="15">
+        <v>2273</v>
+      </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139" s="13">

--- a/판매량(계획_실적).xlsx
+++ b/판매량(계획_실적).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\사업계획_최종\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5966A0BF-2C69-422E-94E2-A5F14C064F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BFBDB1-D62A-46C2-BAA8-FDDAC34F0334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{D128E510-671F-48EF-8073-3332101EE63B}"/>
   </bookViews>
@@ -24170,6 +24170,51 @@
       <c r="C139" s="12">
         <v>6</v>
       </c>
+      <c r="D139" s="15">
+        <v>411.40632870000002</v>
+      </c>
+      <c r="E139" s="15">
+        <v>19578.56279</v>
+      </c>
+      <c r="F139" s="15">
+        <v>394.46750099999997</v>
+      </c>
+      <c r="G139" s="15">
+        <v>128.565</v>
+      </c>
+      <c r="H139" s="15">
+        <v>20513.001619699997</v>
+      </c>
+      <c r="I139" s="15">
+        <v>6155.1082359999991</v>
+      </c>
+      <c r="J139" s="15">
+        <v>556.61820039999998</v>
+      </c>
+      <c r="K139" s="15">
+        <v>2392.2193266000004</v>
+      </c>
+      <c r="L139" s="15">
+        <v>16937.415506199999</v>
+      </c>
+      <c r="M139" s="15">
+        <v>5937</v>
+      </c>
+      <c r="N139" s="15">
+        <v>303</v>
+      </c>
+      <c r="O139" s="15">
+        <v>360.70600000000002</v>
+      </c>
+      <c r="P139" s="15">
+        <v>441.36035379999998</v>
+      </c>
+      <c r="Q139" s="15">
+        <v>11.289</v>
+      </c>
+      <c r="R139" s="15">
+        <v>46.326619800000003</v>
+      </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
@@ -32366,6 +32411,51 @@
       <c r="C139" s="12">
         <v>6</v>
       </c>
+      <c r="D139" s="15">
+        <v>17545</v>
+      </c>
+      <c r="E139" s="15">
+        <v>834338</v>
+      </c>
+      <c r="F139" s="15">
+        <v>16748</v>
+      </c>
+      <c r="G139" s="15">
+        <v>5454</v>
+      </c>
+      <c r="H139" s="15">
+        <v>874085</v>
+      </c>
+      <c r="I139" s="15">
+        <v>261936</v>
+      </c>
+      <c r="J139" s="15">
+        <v>23671</v>
+      </c>
+      <c r="K139" s="15">
+        <v>101633</v>
+      </c>
+      <c r="L139" s="15">
+        <v>719250</v>
+      </c>
+      <c r="M139" s="15">
+        <v>256276</v>
+      </c>
+      <c r="N139" s="15">
+        <v>12797</v>
+      </c>
+      <c r="O139" s="15">
+        <v>15296</v>
+      </c>
+      <c r="P139" s="15">
+        <v>18726</v>
+      </c>
+      <c r="Q139" s="15">
+        <v>479</v>
+      </c>
+      <c r="R139" s="15">
+        <v>1964</v>
+      </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140" s="10">
